--- a/files/港岛-坚尼地城及摩星岭-御海园.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-御海园.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="御海园" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A号屋" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -634,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -644,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2291,6 +2292,48 @@
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>A号屋</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>66A</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>4580</v>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>39301</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2749,4 +2792,120 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>A号屋 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>66A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr"/>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>66A | 4580呎 (4+房)
+$18000万
+$39,301/呎
+(已售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-坚尼地城及摩星岭-御海园.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-御海园.xlsx
@@ -644,7 +644,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-12-23</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-12-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2007-12-11</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-11-05</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-06-20</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-10-24</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-08-02</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2005-09-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-10-24</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2005-11-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-10-24</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-11-05</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2004-12-19</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2522,7 +2522,7 @@
           <t>D | 1774呎 (null房)
 $2672万
 $15,062/呎
-(已售)</t>
+(04年-12月)</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
           <t>B | 1679呎 (4+房)
 $2930万
 $17,451/呎
-(已售)</t>
+(07年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -2561,7 +2561,7 @@
           <t>D | 1307呎 (4+房)
 $1800万
 $13,772/呎
-(已售)</t>
+(04年-12月)</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
           <t>D | 0呎 (null房)
 $2630万
 -
-(已售)</t>
+(04年-11月)</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
           <t>B | 1709呎 (4+房)
 $4638万
 $27,139/呎
-(已售)</t>
+(19年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -2640,7 +2640,7 @@
           <t>A | 0呎 (4+房)
 $1700万
 -
-(已售)</t>
+(05年-09月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2648,7 +2648,7 @@
           <t>B | 1087呎 (3房)
 $1370万
 $12,603/呎
-(已售)</t>
+(04年-08月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -2656,7 +2656,7 @@
           <t>C | 0呎 (3房)
 $1370万
 -
-(已售)</t>
+(04年-10月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -2695,7 +2695,7 @@
           <t>C | 0呎 (3房)
 $1318万
 -
-(已售)</t>
+(04年-10月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -2734,7 +2734,7 @@
           <t>C | 0呎 (3房)
 $1263万
 -
-(已售)</t>
+(04年-10月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -2742,7 +2742,7 @@
           <t>D | 0呎 (4+房)
 $1571万
 -
-(已售)</t>
+(05年-11月)</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2765,7 @@
           <t>B | 1082呎 (null房)
 $1268万
 $11,719/呎
-(已售)</t>
+(04年-12月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -2773,7 +2773,7 @@
           <t>C | 1052呎 (null房)
 $1260万
 $11,977/呎
-(已售)</t>
+(04年-11月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -2897,7 +2897,7 @@
           <t>66A | 4580呎 (4+房)
 $18000万
 $39,301/呎
-(已售)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-坚尼地城及摩星岭-御海园.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-御海园.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="御海园" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A号屋" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -125,6 +125,36 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -202,64 +232,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -269,6 +299,21 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,7 +690,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2303,7 +2348,7 @@
           <t>A号屋</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr"/>
+      <c r="B35" s="3" t="n"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
           <t>66A</t>
@@ -2800,22 +2845,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>A号屋 销控网格图</t>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>御海园 - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
@@ -2846,64 +2891,69 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>66A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr"/>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>66A | 4580呎 (4+房)
-$18000万
-$39,301/呎
-(25年-10月)</t>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A号屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A号屋
+4580呎 (4+房)
+(25年-10月)
+$1.80亿
+$39,301/呎</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-坚尼地城及摩星岭-御海园.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-御海园.xlsx
@@ -235,61 +235,61 @@
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -301,19 +301,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,7 +690,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2348,7 +2348,7 @@
           <t>A号屋</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
+      <c r="B35" s="3" t="inlineStr"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
           <t>66A</t>

--- a/files/港岛-坚尼地城及摩星岭-御海园.xlsx
+++ b/files/港岛-坚尼地城及摩星岭-御海园.xlsx
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1774</v>
+        <v>1880</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>26720000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>15062</v>
+        <v>14213</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1307</v>
+        <v>1363</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>18000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>13772</v>
+        <v>13206</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1679</v>
+        <v>1725</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1679</v>
+        <v>1723</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>29300000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>17451</v>
+        <v>17005</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1307</v>
+        <v>1363</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1307</v>
+        <v>1361</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1292</v>
+        <v>1349</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>13700000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>12603</v>
+        <v>12500</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1335</v>
+        <v>1346</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1052</v>
+        <v>1101</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>12600000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>11977</v>
+        <v>11444</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2564,9 +2564,9 @@
       <c r="D6" s="21" t="inlineStr"/>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>D | 1774呎 (null房)
+          <t>D | 1880呎 (null房)
 $2672万
-$15,062/呎
+$14,213/呎
 (04年-12月)</t>
         </is>
       </c>
@@ -2587,15 +2587,15 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1679呎 (4+房)
+          <t>B | 1723呎 (4+房)
 $2930万
-$17,451/呎
+$17,005/呎
 (07年-12月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 1679呎 (4+房)
+          <t>C | 1725呎 (4+房)
 -
 -
 (待售)</t>
@@ -2603,9 +2603,9 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>D | 1307呎 (4+房)
+          <t>D | 1363呎 (4+房)
 $1800万
-$13,772/呎
+$13,206/呎
 (04年-12月)</t>
         </is>
       </c>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 1307呎 (4+房)
+          <t>A | 1361呎 (4+房)
 -
 -
 (待售)</t>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>D | 1307呎 (4+房)
+          <t>D | 1363呎 (4+房)
 -
 -
 (待售)</t>
@@ -2690,9 +2690,9 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1087呎 (3房)
+          <t>B | 1096呎 (3房)
 $1370万
-$12,603/呎
+$12,500/呎
 (04年-08月)</t>
         </is>
       </c>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>D | 1292呎 (4+房)
+          <t>D | 1349呎 (4+房)
 -
 -
 (待售)</t>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1087呎 (3房)
+          <t>B | 1096呎 (3房)
 -
 -
 (待售)</t>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1335呎 (4+房)
+          <t>A | 1346呎 (4+房)
 -
 -
 (待售)</t>
@@ -2815,9 +2815,9 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>C | 1052呎 (null房)
+          <t>C | 1101呎 (null房)
 $1260万
-$11,977/呎
+$11,444/呎
 (04年-11月)</t>
         </is>
       </c>
